--- a/02-LeetCode/images/普里姆算法过程.xlsx
+++ b/02-LeetCode/images/普里姆算法过程.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10125"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9418F2-D1AE-B34D-8CC5-F3A1DD27101A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,14 +43,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>adjIndex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>lowCost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -120,13 +113,20 @@
   <si>
     <t>{A,C,F,D,B,E}</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>preIndex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dist</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -302,16 +302,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -320,18 +311,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -344,26 +329,38 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -375,14 +372,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -420,7 +420,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -492,7 +492,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -665,401 +665,375 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B5:L18"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="9" style="2"/>
     <col min="3" max="10" width="9" style="1"/>
-    <col min="11" max="11" width="13.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="12.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="13.6640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="2" customWidth="1"/>
     <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="2:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="14" t="s">
+    <row r="5" spans="2:12" ht="15" thickBot="1"/>
+    <row r="6" spans="2:12" ht="15" thickBot="1">
+      <c r="B6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="H6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="I6" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="J6" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="B7" s="20">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="16">
+        <v>2</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="15" thickBot="1">
+      <c r="B8" s="21"/>
+      <c r="C8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <v>6</v>
+      </c>
+      <c r="F8" s="5">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4">
+        <v>5</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="15"/>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" s="20">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1">
+        <v>2</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2</v>
+      </c>
+      <c r="J9" s="16">
+        <v>5</v>
+      </c>
+      <c r="K9" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="L9" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="J6" s="14" t="s">
+    </row>
+    <row r="10" spans="2:12" ht="15" thickBot="1">
+      <c r="B10" s="21"/>
+      <c r="C10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4">
+        <v>5</v>
+      </c>
+      <c r="H10" s="4">
+        <v>6</v>
+      </c>
+      <c r="I10" s="5">
+        <v>4</v>
+      </c>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="15"/>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="B11" s="22">
         <v>3</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="16" t="s">
+      <c r="C11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6">
+        <v>2</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="7">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B7" s="17">
-        <v>1</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0</v>
-      </c>
-      <c r="H7" s="4">
-        <v>0</v>
-      </c>
-      <c r="I7" s="4">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
+      <c r="H11" s="6">
         <v>2</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="19"/>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0</v>
-      </c>
-      <c r="E8" s="7">
-        <v>6</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
-        <v>5</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="20"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B9" s="17">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4">
-        <v>2</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-      <c r="H9" s="4">
-        <v>2</v>
-      </c>
-      <c r="I9" s="6">
-        <v>2</v>
-      </c>
-      <c r="J9" s="3">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="19"/>
-      <c r="C10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7">
-        <v>5</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>5</v>
-      </c>
-      <c r="H10" s="7">
-        <v>6</v>
-      </c>
-      <c r="I10" s="8">
-        <v>4</v>
-      </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="20"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B11" s="21">
-        <v>3</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10">
-        <v>2</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11">
-        <v>5</v>
-      </c>
-      <c r="H11" s="10">
-        <v>2</v>
-      </c>
-      <c r="I11" s="10"/>
+      <c r="I11" s="6"/>
       <c r="J11" s="12">
         <v>3</v>
       </c>
       <c r="K11" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="19"/>
-      <c r="C12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7">
+        <v>17</v>
+      </c>
+      <c r="L11" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="15" thickBot="1">
+      <c r="B12" s="21"/>
+      <c r="C12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
         <v>5</v>
       </c>
-      <c r="F12" s="7">
-        <v>0</v>
-      </c>
-      <c r="G12" s="8">
+      <c r="F12" s="4">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
         <v>2</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="4">
         <v>6</v>
       </c>
-      <c r="I12" s="7">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="20"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B13" s="21">
+      <c r="I12" s="4">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="15"/>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="B13" s="22">
         <v>4</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="11">
+      <c r="C13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="7">
         <v>2</v>
       </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10">
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6">
         <v>2</v>
       </c>
-      <c r="I13" s="10"/>
+      <c r="I13" s="6"/>
       <c r="J13" s="12">
         <v>1</v>
       </c>
       <c r="K13" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="19"/>
-      <c r="C14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="7">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8">
+        <v>19</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="15" thickBot="1">
+      <c r="B14" s="21"/>
+      <c r="C14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5">
         <v>5</v>
       </c>
-      <c r="F14" s="7">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7">
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
         <v>6</v>
       </c>
-      <c r="I14" s="7">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="20"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B15" s="21">
+      <c r="I14" s="4">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="15"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="22">
         <v>5</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="11">
+      <c r="C15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="7">
         <v>1</v>
       </c>
-      <c r="I15" s="10"/>
+      <c r="I15" s="6"/>
       <c r="J15" s="12">
         <v>4</v>
       </c>
       <c r="K15" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="15" thickBot="1">
+      <c r="B16" s="21"/>
+      <c r="C16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="5">
+        <v>3</v>
+      </c>
+      <c r="I16" s="4">
+        <v>0</v>
+      </c>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="15"/>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="B17" s="20">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L15" s="22" t="s">
+      <c r="J17" s="18"/>
+      <c r="K17" s="16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" spans="2:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="19"/>
-      <c r="C16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="7">
-        <v>0</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0</v>
-      </c>
-      <c r="H16" s="8">
-        <v>3</v>
-      </c>
-      <c r="I16" s="7">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="20"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.15">
-      <c r="B17" s="17">
+      <c r="L17" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="3" t="s">
+    </row>
+    <row r="18" spans="2:12" ht="15" thickBot="1">
+      <c r="B18" s="21"/>
+      <c r="C18" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="14.25" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="19"/>
-      <c r="C18" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
-        <v>0</v>
-      </c>
-      <c r="I18" s="7">
-        <v>0</v>
-      </c>
-      <c r="J18" s="23"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="20"/>
+      <c r="D18" s="4">
+        <v>0</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18" s="19"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="J15:J16"/>
     <mergeCell ref="J17:J18"/>
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="B9:B10"/>
@@ -1067,6 +1041,23 @@
     <mergeCell ref="B13:B14"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="B17:B18"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="L17:L18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1075,9 +1066,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1085,9 +1076,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
